--- a/artfynd/A 10546-2023 artfynd.xlsx
+++ b/artfynd/A 10546-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10546-2023 artfynd.xlsx
+++ b/artfynd/A 10546-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7242780</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618358.2989171504</v>
+        <v>618358</v>
       </c>
       <c r="R2" t="n">
-        <v>7107594.363209431</v>
+        <v>7107594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,12 +792,7 @@
         <v>7242779</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>618675.0102403538</v>
+        <v>618675</v>
       </c>
       <c r="R3" t="n">
-        <v>7107524.53571468</v>
+        <v>7107525</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +857,9 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,12 +906,7 @@
         <v>7242781</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618523.5644801188</v>
+        <v>618524</v>
       </c>
       <c r="R4" t="n">
-        <v>7107550.729517716</v>
+        <v>7107551</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,19 +971,9 @@
           <t>2013-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 10546-2023 artfynd.xlsx
+++ b/artfynd/A 10546-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,125 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134600630</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>618339</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7107590</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Sture Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 10546-2023 artfynd.xlsx
+++ b/artfynd/A 10546-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134600630</v>
+        <v>134769750</v>
       </c>
       <c r="B5" t="n">
-        <v>57386</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102954</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,27 +1046,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Pellemyrtjärnen, Ås lm</t>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>618339</v>
+        <v>618253</v>
       </c>
       <c r="R5" t="n">
-        <v>7107590</v>
+        <v>7107561</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,22 +1082,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:16</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,15 +1107,344 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134769868</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>618287</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7107544</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134769899</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>618338</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7107537</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökande hona i hyggeskant,</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134600630</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Pellemyrtjärnen, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>618339</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7107590</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Alva Danielsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Alva Danielsson, Sture Gustafsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>

--- a/artfynd/A 10546-2023 artfynd.xlsx
+++ b/artfynd/A 10546-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242780</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242779</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7242781</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769750</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769868</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134769899</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,8 +1484,22 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134600630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>